--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MONBUS OBRADOIRO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MONBUS OBRADOIRO.xlsx
@@ -565,13 +565,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>98.3349</v>
+        <v>106.4814</v>
       </c>
       <c r="E2" t="n">
-        <v>89.2681</v>
+        <v>91.77379999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>9.066800000000001</v>
+        <v>14.7079</v>
       </c>
       <c r="G2" t="n">
         <v>44.1315</v>
@@ -610,13 +610,13 @@
         <v>57.6391</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.906</v>
+        <v>4.2405</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1961000000000001</v>
+        <v>2.7017</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.1024</v>
+        <v>1.5387</v>
       </c>
       <c r="V2" t="n">
         <v>35.9235</v>
@@ -643,13 +643,13 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>92.551</v>
+        <v>74.19329999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>78.15600000000001</v>
+        <v>60.563</v>
       </c>
       <c r="F3" t="n">
-        <v>14.3957</v>
+        <v>13.6301</v>
       </c>
       <c r="G3" t="n">
         <v>35.0369</v>
@@ -688,13 +688,13 @@
         <v>58.5095</v>
       </c>
       <c r="S3" t="n">
-        <v>36.0487</v>
+        <v>17.6908</v>
       </c>
       <c r="T3" t="n">
-        <v>28.3652</v>
+        <v>10.7723</v>
       </c>
       <c r="U3" t="n">
-        <v>7.6834</v>
+        <v>6.9185</v>
       </c>
       <c r="V3" t="n">
         <v>4.5</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>65.4586</v>
+        <v>60.06950000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>38.0472</v>
+        <v>26.4099</v>
       </c>
       <c r="F4" t="n">
-        <v>27.4115</v>
+        <v>33.6597</v>
       </c>
       <c r="G4" t="n">
-        <v>38.5937</v>
+        <v>31.5449</v>
       </c>
       <c r="H4" t="n">
-        <v>32.2007</v>
+        <v>26.597</v>
       </c>
       <c r="I4" t="n">
-        <v>6.3929</v>
+        <v>4.947700000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>48.1479</v>
+        <v>42.4957</v>
       </c>
       <c r="K4" t="n">
-        <v>34.5698</v>
+        <v>27.0231</v>
       </c>
       <c r="L4" t="n">
-        <v>13.5781</v>
+        <v>15.4728</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.5542</v>
+        <v>-10.9508</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3686</v>
+        <v>-0.4263000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.1855</v>
+        <v>-10.5248</v>
       </c>
       <c r="P4" t="n">
-        <v>7.8301</v>
+        <v>19.793</v>
       </c>
       <c r="Q4" t="n">
-        <v>-33.0607</v>
+        <v>-38.0635</v>
       </c>
       <c r="R4" t="n">
-        <v>40.8909</v>
+        <v>57.857</v>
       </c>
       <c r="S4" t="n">
-        <v>27.8887</v>
+        <v>4.6116</v>
       </c>
       <c r="T4" t="n">
-        <v>20.144</v>
+        <v>2.0793</v>
       </c>
       <c r="U4" t="n">
-        <v>7.744400000000001</v>
+        <v>2.5325</v>
       </c>
       <c r="V4" t="n">
-        <v>-8.853899999999999</v>
+        <v>4.1199</v>
       </c>
       <c r="W4" t="n">
-        <v>2.815999999999999</v>
+        <v>19.8987</v>
       </c>
       <c r="X4" t="n">
-        <v>-11.6701</v>
+        <v>-15.779</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>54.1498</v>
+        <v>50.8217</v>
       </c>
       <c r="E5" t="n">
-        <v>20.5264</v>
+        <v>25.9375</v>
       </c>
       <c r="F5" t="n">
-        <v>33.6235</v>
+        <v>24.8842</v>
       </c>
       <c r="G5" t="n">
-        <v>31.5449</v>
+        <v>38.5937</v>
       </c>
       <c r="H5" t="n">
-        <v>26.597</v>
+        <v>32.2007</v>
       </c>
       <c r="I5" t="n">
-        <v>4.947700000000001</v>
+        <v>6.3929</v>
       </c>
       <c r="J5" t="n">
-        <v>42.4957</v>
+        <v>48.1479</v>
       </c>
       <c r="K5" t="n">
-        <v>27.0231</v>
+        <v>34.5698</v>
       </c>
       <c r="L5" t="n">
-        <v>15.4728</v>
+        <v>13.5781</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.9508</v>
+        <v>-9.5542</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4263000000000001</v>
+        <v>-2.3686</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.5248</v>
+        <v>-7.1855</v>
       </c>
       <c r="P5" t="n">
-        <v>19.793</v>
+        <v>7.8301</v>
       </c>
       <c r="Q5" t="n">
-        <v>-38.0635</v>
+        <v>-33.0607</v>
       </c>
       <c r="R5" t="n">
-        <v>57.857</v>
+        <v>40.8909</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3078</v>
+        <v>13.2519</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.8046</v>
+        <v>8.034800000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4964</v>
+        <v>5.2173</v>
       </c>
       <c r="V5" t="n">
-        <v>4.1199</v>
+        <v>-8.853899999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>19.8987</v>
+        <v>2.815999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-15.779</v>
+        <v>-11.6701</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>46.8321</v>
+        <v>49.0135</v>
       </c>
       <c r="E6" t="n">
-        <v>43.3871</v>
+        <v>43.8878</v>
       </c>
       <c r="F6" t="n">
-        <v>3.445400000000002</v>
+        <v>5.125599999999999</v>
       </c>
       <c r="G6" t="n">
         <v>9.223900000000004</v>
@@ -922,13 +922,13 @@
         <v>58.292</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4696</v>
+        <v>5.6512</v>
       </c>
       <c r="T6" t="n">
-        <v>2.398699999999999</v>
+        <v>2.9001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0707</v>
+        <v>2.7512</v>
       </c>
       <c r="V6" t="n">
         <v>-1.315</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6351</v>
+        <v>44.887</v>
       </c>
       <c r="E7" t="n">
-        <v>3.310000000000001</v>
+        <v>32.7605</v>
       </c>
       <c r="F7" t="n">
-        <v>31.3256</v>
+        <v>12.1263</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.420699999999999</v>
+        <v>68.55710000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1145</v>
+        <v>20.2761</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.5349</v>
+        <v>48.2813</v>
       </c>
       <c r="J7" t="n">
-        <v>11.5773</v>
+        <v>97.81059999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>6.9668</v>
+        <v>30.3714</v>
       </c>
       <c r="L7" t="n">
-        <v>4.610000000000001</v>
+        <v>67.44</v>
       </c>
       <c r="M7" t="n">
-        <v>-13.9978</v>
+        <v>-29.254</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8524</v>
+        <v>-10.0951</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.1456</v>
+        <v>-19.1589</v>
       </c>
       <c r="P7" t="n">
-        <v>15.6605</v>
+        <v>-37.8462</v>
       </c>
       <c r="Q7" t="n">
-        <v>-41.7612</v>
+        <v>-94.3977</v>
       </c>
       <c r="R7" t="n">
-        <v>57.422</v>
+        <v>56.5519</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6039000000000003</v>
+        <v>4.0572</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9673</v>
+        <v>0.9531999999999998</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5709</v>
+        <v>3.104</v>
       </c>
       <c r="V7" t="n">
-        <v>20.7914</v>
+        <v>10.1181</v>
       </c>
       <c r="W7" t="n">
-        <v>35.4609</v>
+        <v>28.3941</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.6693</v>
+        <v>-18.2757</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>29.5841</v>
+        <v>40.4055</v>
       </c>
       <c r="E8" t="n">
-        <v>16.5084</v>
+        <v>7.671900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>13.0756</v>
+        <v>32.7333</v>
       </c>
       <c r="G8" t="n">
-        <v>2.279700000000001</v>
+        <v>-2.420699999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>13.5544</v>
+        <v>4.1145</v>
       </c>
       <c r="I8" t="n">
-        <v>-11.2748</v>
+        <v>-6.5349</v>
       </c>
       <c r="J8" t="n">
-        <v>18.8777</v>
+        <v>11.5773</v>
       </c>
       <c r="K8" t="n">
-        <v>17.5167</v>
+        <v>6.9668</v>
       </c>
       <c r="L8" t="n">
-        <v>1.360700000000001</v>
+        <v>4.610000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-16.5981</v>
+        <v>-13.9978</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.9626</v>
+        <v>-2.8524</v>
       </c>
       <c r="O8" t="n">
-        <v>-12.6356</v>
+        <v>-11.1456</v>
       </c>
       <c r="P8" t="n">
-        <v>35.8883</v>
+        <v>15.6605</v>
       </c>
       <c r="Q8" t="n">
-        <v>-15.4427</v>
+        <v>-41.7612</v>
       </c>
       <c r="R8" t="n">
-        <v>51.3314</v>
+        <v>57.422</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.2323</v>
+        <v>6.374</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.3733</v>
+        <v>2.3954</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1403999999999999</v>
+        <v>3.9791</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.3522</v>
+        <v>20.7914</v>
       </c>
       <c r="W8" t="n">
-        <v>16.4467</v>
+        <v>35.4609</v>
       </c>
       <c r="X8" t="n">
-        <v>-21.7989</v>
+        <v>-14.6693</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28.9207</v>
+        <v>39.7785</v>
       </c>
       <c r="E9" t="n">
-        <v>24.1503</v>
+        <v>34.0072</v>
       </c>
       <c r="F9" t="n">
-        <v>4.769399999999999</v>
+        <v>5.771700000000001</v>
       </c>
       <c r="G9" t="n">
         <v>8.6318</v>
@@ -1156,13 +1156,13 @@
         <v>53.5069</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.220599999999999</v>
+        <v>8.637</v>
       </c>
       <c r="T9" t="n">
-        <v>-5.6727</v>
+        <v>4.1831</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4522</v>
+        <v>4.4539</v>
       </c>
       <c r="V9" t="n">
         <v>-5.3317</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>27.8051</v>
+        <v>34.8932</v>
       </c>
       <c r="E10" t="n">
-        <v>18.3398</v>
+        <v>20.0451</v>
       </c>
       <c r="F10" t="n">
-        <v>9.4648</v>
+        <v>14.8485</v>
       </c>
       <c r="G10" t="n">
-        <v>68.55710000000001</v>
+        <v>2.279700000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>20.2761</v>
+        <v>13.5544</v>
       </c>
       <c r="I10" t="n">
-        <v>48.2813</v>
+        <v>-11.2748</v>
       </c>
       <c r="J10" t="n">
-        <v>97.81059999999999</v>
+        <v>18.8777</v>
       </c>
       <c r="K10" t="n">
-        <v>30.3714</v>
+        <v>17.5167</v>
       </c>
       <c r="L10" t="n">
-        <v>67.44</v>
+        <v>1.360700000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-29.254</v>
+        <v>-16.5981</v>
       </c>
       <c r="N10" t="n">
-        <v>-10.0951</v>
+        <v>-3.9626</v>
       </c>
       <c r="O10" t="n">
-        <v>-19.1589</v>
+        <v>-12.6356</v>
       </c>
       <c r="P10" t="n">
-        <v>-37.8462</v>
+        <v>35.8883</v>
       </c>
       <c r="Q10" t="n">
-        <v>-94.3977</v>
+        <v>-15.4427</v>
       </c>
       <c r="R10" t="n">
-        <v>56.5519</v>
+        <v>51.3314</v>
       </c>
       <c r="S10" t="n">
-        <v>-13.0243</v>
+        <v>2.0772</v>
       </c>
       <c r="T10" t="n">
-        <v>-13.467</v>
+        <v>0.1635999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4428000000000004</v>
+        <v>1.9132</v>
       </c>
       <c r="V10" t="n">
-        <v>10.1181</v>
+        <v>-5.3522</v>
       </c>
       <c r="W10" t="n">
-        <v>28.3941</v>
+        <v>16.4467</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.2757</v>
+        <v>-21.7989</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>21.5061</v>
+        <v>22.3686</v>
       </c>
       <c r="E11" t="n">
-        <v>12.5798</v>
+        <v>12.5687</v>
       </c>
       <c r="F11" t="n">
-        <v>8.9261</v>
+        <v>9.7996</v>
       </c>
       <c r="G11" t="n">
         <v>10.6918</v>
@@ -1312,13 +1312,13 @@
         <v>24.5786</v>
       </c>
       <c r="S11" t="n">
-        <v>7.1053</v>
+        <v>7.968</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5919</v>
+        <v>3.5812</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5132</v>
+        <v>4.3871</v>
       </c>
       <c r="V11" t="n">
         <v>-8.906699999999999</v>
@@ -1345,13 +1345,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11.5434</v>
+        <v>12.625</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6053</v>
+        <v>3.4452</v>
       </c>
       <c r="F12" t="n">
-        <v>8.938400000000001</v>
+        <v>9.1799</v>
       </c>
       <c r="G12" t="n">
         <v>14.1124</v>
@@ -1390,13 +1390,13 @@
         <v>20.6632</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0073</v>
+        <v>3.0887</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1780999999999999</v>
+        <v>1.0181</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8292</v>
+        <v>2.0708</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2261</v>
@@ -1423,13 +1423,13 @@
         <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>10.0322</v>
+        <v>9.0008</v>
       </c>
       <c r="E13" t="n">
-        <v>9.3453</v>
+        <v>6.937</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6871000000000002</v>
+        <v>2.0638</v>
       </c>
       <c r="G13" t="n">
         <v>12.4244</v>
@@ -1468,13 +1468,13 @@
         <v>15.6602</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2261</v>
+        <v>-3.2574</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5431</v>
+        <v>-0.8652000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.7693</v>
+        <v>-2.3924</v>
       </c>
       <c r="V13" t="n">
         <v>-9.9537</v>
@@ -1501,13 +1501,13 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7.769599999999999</v>
+        <v>8.8688</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3936</v>
+        <v>7.3128</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3761</v>
+        <v>1.5559</v>
       </c>
       <c r="G14" t="n">
         <v>8.117900000000001</v>
@@ -1546,13 +1546,13 @@
         <v>8.2652</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3255</v>
+        <v>0.7734999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1778</v>
+        <v>-0.2584</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8521000000000001</v>
+        <v>1.0319</v>
       </c>
       <c r="V14" t="n">
         <v>1.4997</v>
@@ -1579,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1183000000000005</v>
+        <v>0.2902</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6698</v>
+        <v>-1.4463</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5515</v>
+        <v>1.7364</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6401</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4113</v>
+        <v>-1.0027</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0445</v>
+        <v>0.179</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3668</v>
+        <v>-1.1819</v>
       </c>
       <c r="V15" t="n">
         <v>1.7156</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9078</v>
+        <v>-1.8885</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.649</v>
+        <v>-0.5372</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2588</v>
+        <v>-1.3513</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0326</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4402</v>
+        <v>-0.4209</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1662</v>
+        <v>-0.2587</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2271</v>
+        <v>-3.3196</v>
       </c>
       <c r="E18" t="n">
         <v>-0.9825</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2445</v>
+        <v>-2.337</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4775</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1422</v>
+        <v>-0.2346</v>
       </c>
       <c r="T18" t="n">
         <v>-0.274</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1318</v>
+        <v>0.0394</v>
       </c>
       <c r="V18" t="n">
         <v>-2.8249</v>
@@ -1891,13 +1891,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.959999999999997</v>
+        <v>-7.6397</v>
       </c>
       <c r="E19" t="n">
-        <v>-13.1269</v>
+        <v>-11.3822</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1668</v>
+        <v>3.7423</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3790999999999995</v>
@@ -1936,13 +1936,13 @@
         <v>9.5702</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.4308</v>
+        <v>-2.1105</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.5824</v>
+        <v>-1.8373</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8487</v>
+        <v>-0.2732</v>
       </c>
       <c r="V19" t="n">
         <v>-4.7152</v>
@@ -1969,13 +1969,13 @@
         <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>513.527</v>
+        <v>540.4667000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>346.1891</v>
+        <v>358.9722</v>
       </c>
       <c r="F20" t="n">
-        <v>167.3385</v>
+        <v>181.4944</v>
       </c>
       <c r="G20" t="n">
         <v>278.0135</v>
@@ -1987,7 +1987,7 @@
         <v>69.6365</v>
       </c>
       <c r="J20" t="n">
-        <v>488.8156000000001</v>
+        <v>488.8156</v>
       </c>
       <c r="K20" t="n">
         <v>270.7606</v>
@@ -1999,7 +1999,7 @@
         <v>-210.8032</v>
       </c>
       <c r="N20" t="n">
-        <v>-62.385</v>
+        <v>-62.38500000000001</v>
       </c>
       <c r="O20" t="n">
         <v>-148.4181</v>
@@ -2014,13 +2014,13 @@
         <v>574.2182</v>
       </c>
       <c r="S20" t="n">
-        <v>44.4564</v>
+        <v>71.3955</v>
       </c>
       <c r="T20" t="n">
-        <v>22.77949999999999</v>
+        <v>35.5647</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6741</v>
+        <v>35.8314</v>
       </c>
       <c r="V20" t="n">
         <v>31.1888</v>
